--- a/week-3/day-2/data_driven_api/users.xlsx
+++ b/week-3/day-2/data_driven_api/users.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nishi\RJP\Python_handson\week-3\day-2\data_driven_api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DAC2F4-85B3-4D1B-B930-5AAFD730CA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BF8538-2912-410C-9114-942292884257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="product" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>name</t>
   </si>
@@ -61,6 +62,30 @@
   </si>
   <si>
     <t>emma@test.com</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart watch </t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>L123</t>
+  </si>
+  <si>
+    <t>M345</t>
+  </si>
+  <si>
+    <t>Sw123</t>
+  </si>
+  <si>
+    <t>prize</t>
   </si>
 </sst>
 </file>
@@ -465,4 +490,63 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CD3937-559E-4DD5-BD73-C79C6AD5373E}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.6328125" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="3" max="3" width="21.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/week-3/day-2/data_driven_api/users.xlsx
+++ b/week-3/day-2/data_driven_api/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nishi\RJP\Python_handson\week-3\day-2\data_driven_api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BF8538-2912-410C-9114-942292884257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694BE7EA-0516-4430-867B-1C165C317C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>name</t>
   </si>
@@ -73,9 +73,6 @@
     <t xml:space="preserve">Smart watch </t>
   </si>
   <si>
-    <t>version</t>
-  </si>
-  <si>
     <t>L123</t>
   </si>
   <si>
@@ -85,7 +82,13 @@
     <t>Sw123</t>
   </si>
   <si>
-    <t>prize</t>
+    <t>A(username)</t>
+  </si>
+  <si>
+    <t>B(job)</t>
+  </si>
+  <si>
+    <t>C(expected_status)</t>
   </si>
 </sst>
 </file>
@@ -497,20 +500,20 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.6328125" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="21.6328125" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" customWidth="1"/>
+    <col min="3" max="3" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -518,7 +521,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3">
         <v>78000</v>
@@ -529,7 +532,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3">
         <v>34000</v>
@@ -540,7 +543,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3">
         <v>5000</v>
